--- a/workflows/order-logistics-query-flow/out/物流查询台账.xlsx
+++ b/workflows/order-logistics-query-flow/out/物流查询台账.xlsx
@@ -435,11 +435,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -651,50 +651,142 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>JD0033112255667</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>京东物流</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TB20260926018</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>已签收</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:40</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>您的包裹已签收，签收人：本人</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>包裹已显示签收。若您本人未收到，可能是门卫/驿站代收，请先核实；仍无果我们即刻为您发起查件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>EMS9988776655443</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>EMS</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>TB20260915006</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>运输中</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>2026-09-19 10:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>邮件到达乌鲁木齐中心，发往喀什</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>263</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>⚠️ 异常</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>超 72 小时无更新</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>包裹正在运输途中，会按面单路线中转，到达派件网点后会更新「派件中」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>YUNDA7711223344</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>韵达</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TB20260929044</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待揽收</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>快件待揽收</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>您的订单已下单，仓库正在打包，预计 48 小时内揽收，如有延迟我们会主动同步。</t>
         </is>
       </c>
     </row>
